--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Device welches die eMed Fachanwendung abbildet</t>
+    <t>Das Device, welches die eMed Fachanwendung abbildet</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$79</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2774" uniqueCount="430">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +282,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -311,14 +314,191 @@
 </t>
   </si>
   <si>
-    <t>Device.implicitRules</t>
+    <t>Device.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Device.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Device.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Device.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Device.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Device.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -384,6 +564,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>Device.text.id</t>
+  </si>
+  <si>
+    <t>Device.text.extension</t>
+  </si>
+  <si>
+    <t>Device.text.status</t>
+  </si>
+  <si>
+    <t>Siehe Notes - "Regeln für den Inhalt der narrativen Teile in den Notes".</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Device.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>Device.contained</t>
   </si>
   <si>
@@ -407,47 +640,22 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Device.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Device.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -513,29 +721,7 @@
     <t>Device.udiCarrier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -550,6 +736,9 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -681,9 +870,6 @@
     <t>Supports a way to distinguish hand entered from machine read data.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
@@ -733,9 +919,6 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
@@ -912,9 +1095,6 @@
   </si>
   <si>
     <t>The kind or type of device.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes to identify medical devices.</t>
@@ -1314,6 +1494,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1495,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.234375" customWidth="true" bestFit="true"/>
@@ -1508,7 +1703,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="27.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1522,11 +1717,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="36.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1657,7 +1852,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1779,13 +1974,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -1896,7 +2091,7 @@
         <v>84</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -1986,7 +2181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -2008,10 +2203,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>98</v>
@@ -2022,9 +2217,7 @@
       <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2073,23 +2266,23 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AG5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL5" t="s" s="2">
         <v>21</v>
       </c>
@@ -2097,7 +2290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -2106,14 +2299,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2125,16 +2318,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2160,46 +2353,46 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>21</v>
@@ -2208,16 +2401,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2233,10 +2426,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>115</v>
@@ -2310,32 +2503,32 @@
         <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AL7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2344,19 +2537,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2406,22 +2599,22 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>21</v>
@@ -2430,23 +2623,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2455,19 +2648,19 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2517,22 +2710,22 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>21</v>
@@ -2543,46 +2736,44 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2630,7 +2821,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2642,10 +2833,10 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>21</v>
@@ -2654,12 +2845,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2679,19 +2870,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2717,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2741,7 +2932,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2756,21 +2947,21 @@
         <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2781,7 +2972,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2790,18 +2981,20 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -2826,13 +3019,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2850,13 +3043,13 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -2874,12 +3067,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2890,19 +3083,19 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>155</v>
@@ -2961,13 +3154,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -2976,16 +3169,16 @@
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>159</v>
       </c>
@@ -3021,7 +3214,9 @@
       <c r="M14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="N14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3046,13 +3241,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3070,7 +3265,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3082,10 +3277,10 @@
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -3096,24 +3291,24 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3122,16 +3317,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3181,22 +3376,22 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
@@ -3205,48 +3400,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3294,22 +3485,22 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
@@ -3318,23 +3509,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3343,18 +3534,20 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3391,62 +3584,62 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3455,13 +3648,13 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3488,13 +3681,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3512,10 +3705,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -3527,13 +3720,13 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -3549,13 +3742,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -3564,18 +3757,18 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
         <v>189</v>
       </c>
+      <c r="N19" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3623,10 +3816,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>84</v>
@@ -3635,10 +3828,10 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
@@ -3647,23 +3840,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3672,19 +3865,19 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3734,47 +3927,47 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3783,19 +3976,19 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3845,36 +4038,36 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>203</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3885,30 +4078,28 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3932,13 +4123,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -3956,22 +4147,22 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3980,12 +4171,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3996,28 +4187,28 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4028,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>21</v>
@@ -4043,13 +4234,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4067,13 +4258,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4082,21 +4273,21 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4107,7 +4298,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4119,13 +4310,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4152,13 +4343,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4176,13 +4367,13 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
@@ -4194,29 +4385,29 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4225,19 +4416,19 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4287,13 +4478,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4302,21 +4493,21 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4339,13 +4530,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>99</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>100</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4396,7 +4587,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4408,35 +4599,35 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4448,15 +4639,17 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>106</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4505,68 +4698,72 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>112</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4614,40 +4811,40 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>248</v>
+        <v>185</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4663,16 +4860,16 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4723,7 +4920,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4738,25 +4935,25 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4775,17 +4972,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4834,7 +5029,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4849,21 +5044,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4874,7 +5069,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -4886,16 +5081,18 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4943,13 +5140,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -4958,7 +5155,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
@@ -4967,16 +5164,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4992,18 +5189,20 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5052,7 +5251,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5064,35 +5263,35 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5101,19 +5300,19 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5163,71 +5362,69 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5252,13 +5449,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5276,22 +5473,22 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>172</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5300,20 +5497,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
@@ -5322,21 +5519,23 @@
         <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5346,7 +5545,7 @@
         <v>21</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>21</v>
@@ -5361,13 +5560,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5385,10 +5584,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>84</v>
@@ -5400,21 +5599,21 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5422,10 +5621,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5437,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>281</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5470,13 +5669,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5494,13 +5693,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5509,25 +5708,25 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5546,15 +5745,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5603,7 +5804,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5618,21 +5819,21 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5655,17 +5856,15 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5714,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5729,21 +5928,21 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5766,13 +5965,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5799,13 +5998,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -5823,7 +6022,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5838,21 +6037,21 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5863,7 +6062,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -5875,13 +6074,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>154</v>
+        <v>298</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5932,13 +6131,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -5947,21 +6146,21 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5984,13 +6183,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6041,7 +6240,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6053,35 +6252,35 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6093,16 +6292,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>131</v>
+        <v>312</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>166</v>
+        <v>313</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>133</v>
+        <v>314</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6152,40 +6351,40 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6198,26 +6397,22 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>170</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6265,7 +6460,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6277,10 +6472,10 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6289,20 +6484,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>84</v>
@@ -6317,13 +6512,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>99</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>100</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6374,10 +6569,10 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>84</v>
@@ -6386,10 +6581,10 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6398,23 +6593,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6426,15 +6621,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>297</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6483,40 +6680,40 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>112</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6529,22 +6726,26 @@
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6592,7 +6793,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6604,10 +6805,10 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6616,20 +6817,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>84</v>
@@ -6644,13 +6845,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>162</v>
+        <v>325</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6701,10 +6902,10 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>163</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>84</v>
@@ -6713,10 +6914,10 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -6725,23 +6926,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6753,17 +6954,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -6788,13 +6987,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -6812,72 +7011,68 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>167</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>164</v>
+        <v>331</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -6925,40 +7120,40 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>172</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6977,15 +7172,17 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7034,7 +7231,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7049,21 +7246,21 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7086,13 +7283,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7119,13 +7316,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7143,7 +7340,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7161,18 +7358,18 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7180,10 +7377,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7195,13 +7392,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7252,13 +7449,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7276,12 +7473,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7292,7 +7489,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7304,13 +7501,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>315</v>
+        <v>99</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>316</v>
+        <v>100</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7361,22 +7558,22 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>314</v>
+        <v>101</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7385,23 +7582,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7413,15 +7610,17 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7470,22 +7669,22 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7494,16 +7693,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7516,24 +7715,26 @@
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>131</v>
+        <v>229</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -7581,7 +7782,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7593,10 +7794,10 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -7605,48 +7806,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>169</v>
+        <v>323</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>170</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7694,22 +7891,22 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -7718,12 +7915,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7731,7 +7928,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>84</v>
@@ -7746,13 +7943,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7803,10 +8000,10 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>84</v>
@@ -7821,18 +8018,18 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7855,13 +8052,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>324</v>
+        <v>220</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7912,7 +8109,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7936,12 +8133,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7952,7 +8149,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -7964,13 +8161,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8021,22 +8218,22 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>327</v>
+        <v>101</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
@@ -8045,23 +8242,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8073,18 +8270,18 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8132,68 +8329,72 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>335</v>
+        <v>102</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>339</v>
+        <v>229</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8241,47 +8442,47 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>337</v>
+        <v>232</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>341</v>
+        <v>185</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8293,17 +8494,15 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8352,13 +8551,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -8367,21 +8566,21 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8404,18 +8603,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>350</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8463,7 +8660,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8478,21 +8675,21 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>355</v>
+        <v>238</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8500,7 +8697,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>84</v>
@@ -8518,14 +8715,12 @@
         <v>98</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -8574,10 +8769,10 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>84</v>
@@ -8589,21 +8784,21 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8626,13 +8821,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>362</v>
+        <v>220</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8683,7 +8878,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8698,7 +8893,7 @@
         <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
@@ -8707,12 +8902,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8723,7 +8918,7 @@
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -8732,16 +8927,16 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>99</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
+        <v>100</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8792,22 +8987,22 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
@@ -8816,23 +9011,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -8844,15 +9039,17 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>370</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>371</v>
+        <v>106</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -8901,31 +9098,1369 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>112</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AK67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM79">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI78">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5497,7 +5497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>271</v>
       </c>
@@ -5510,13 +5510,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>85</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>At ELGA e-Medikation Device Fachanwendung</t>
+    <t>AT ELGA e-Medikation Device Fachanwendung</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
